--- a/quality_surveys/033_production_testing_summary_report--quality_surveys.xlsx
+++ b/quality_surveys/033_production_testing_summary_report--quality_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>production_testing_summary_report</t>
+          <t>production_testing_summary_report_title</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Production Testing Summary Report</t>
+          <t>Production Testing Summary Report Title</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>test_run_id</t>
+          <t>Test Run ID</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>batch_id</t>
+          <t>Batch ID</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>product_id</t>
+          <t>Product ID</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>test_outcome</t>
+          <t>Test Outcome</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>test_outcome_other</t>
+          <t>Test Outcome Other</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>shift</t>
+          <t>Shift</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>start_time</t>
+          <t>Start Time</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>end_time</t>
+          <t>End Time</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>test_duration</t>
+          <t>Test Duration</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>test_date</t>
+          <t>Test Date</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>production_test_summary_notes</t>
+          <t>Production Test Summary Notes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>production_test_summary</t>
+          <t>Production Test Summary</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>production_test_summary_notes</t>
+          <t>test_summary_other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>production_test_summary_notes</t>
+          <t>Test Summary Other</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>production_test_summary_other_notes</t>
+          <t>Production Test Summary Other Notes</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,223 +865,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>production_test_summary_other</t>
+          <t>test_summary_other_other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>production_test_summary_other</t>
+          <t>Test Summary Other Other</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>production_test_summary_other</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>production_test_summary_other</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>production_test_summary_notes_other</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>production_test_summary_notes_other</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>test_summary_other</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>test_summary_other</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>test_summary_other</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>test_summary_other</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>test_outcome_other</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>test_outcome_other</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>test_outcome_other_other</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>test_outcome_other_other</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>test_outcome_other_other</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>test_outcome_other_other</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>test_outcome_other_other_other</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>test_outcome_other_other_other</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>test_outcome_other_other_other_other</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>test_outcome_other_other_other_other</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
